--- a/Computational results FINAL v4.xlsx
+++ b/Computational results FINAL v4.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="518" uniqueCount="371">
   <si>
     <t xml:space="preserve">SpOC-3 Torso Decompositions — computational results</t>
   </si>
@@ -1153,6 +1153,15 @@
   </si>
   <si>
     <t xml:space="preserve">robustness.py block E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESA's own evaluation code, run beside esa_eval.py</t>
+  </si>
+  <si>
+    <t xml:space="preserve">identical on all ten instances: fitness on 220 orderings (44 over the cap), hypervolume on 2,000 point sets, and the min-degree ×8 column reproduced; data/ graphs byte-identical to ESA's</t>
+  </si>
+  <si>
+    <t xml:space="preserve">harness/esa_crosscheck.py, esa_crosscheck.log</t>
   </si>
 </sst>
 </file>
@@ -7430,7 +7439,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5.51"/>
@@ -7981,7 +7990,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="115" t="n">
         <v>26</v>
       </c>
@@ -8059,6 +8068,26 @@
       </c>
       <c r="F33" s="113" t="s">
         <v>367</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="115" t="n">
+        <v>30</v>
+      </c>
+      <c r="B34" s="116" t="s">
+        <v>362</v>
+      </c>
+      <c r="C34" s="116" t="s">
+        <v>368</v>
+      </c>
+      <c r="D34" s="116" t="s">
+        <v>369</v>
+      </c>
+      <c r="E34" s="117" t="s">
+        <v>263</v>
+      </c>
+      <c r="F34" s="116" t="s">
+        <v>370</v>
       </c>
     </row>
   </sheetData>
